--- a/sample_input/sales_q2.xlsx
+++ b/sample_input/sales_q2.xlsx
@@ -644,11 +644,7 @@
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Duplicate entry</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Sales</t>
